--- a/real_estate_forms/010_house_appraisal_checklist_form--real_estate_forms.xlsx
+++ b/real_estate_forms/010_house_appraisal_checklist_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'single_family',_'value':_'single_family'}</t>
+          <t>single_family</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Single Family', 'value': 'Single Family'}</t>
+          <t>Single Family</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'condo',_'value':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Condo', 'value': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'townhouse',_'value':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Townhouse', 'value': 'Townhouse'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'multi-family',_'value':_'multi-family'}</t>
+          <t>multi-family</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Multi-Family', 'value': 'Multi-Family'}</t>
+          <t>Multi-Family</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active', 'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sold',_'value':_'sold'}</t>
+          <t>sold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sold', 'value': 'Sold'}</t>
+          <t>Sold</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'under_contract',_'value':_'under_contract'}</t>
+          <t>under_contract</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Under Contract', 'value': 'Under Contract'}</t>
+          <t>Under Contract</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'primary_residence',_'value':_'primary_residence'}</t>
+          <t>primary_residence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Primary Residence', 'value': 'Primary Residence'}</t>
+          <t>Primary Residence</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'investment',_'value':_'investment'}</t>
+          <t>investment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Investment', 'value': 'Investment'}</t>
+          <t>Investment</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rental',_'value':_'rental'}</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rental', 'value': 'Rental'}</t>
+          <t>Rental</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'residential',_'value':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Residential', 'value': 'Residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'commercial',_'value':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Commercial', 'value': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'industrial',_'value':_'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Industrial', 'value': 'Industrial'}</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gable',_'value':_'gable'}</t>
+          <t>gable</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Gable', 'value': 'Gable'}</t>
+          <t>Gable</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hip',_'value':_'hip'}</t>
+          <t>hip</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hip', 'value': 'Hip'}</t>
+          <t>Hip</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'flat',_'value':_'flat'}</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Flat', 'value': 'Flat'}</t>
+          <t>Flat</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full_basement',_'value':_'full_basement'}</t>
+          <t>full_basement</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full Basement', 'value': 'Full Basement'}</t>
+          <t>Full Basement</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'crawl_space',_'value':_'crawl_space'}</t>
+          <t>crawl_space</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Crawl Space', 'value': 'Crawl Space'}</t>
+          <t>Crawl Space</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pier_and_beam',_'value':_'pier_and_beam'}</t>
+          <t>pier_and_beam</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pier and Beam', 'value': 'Pier and Beam'}</t>
+          <t>Pier and Beam</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'slab',_'value':_'slab'}</t>
+          <t>slab</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Slab', 'value': 'Slab'}</t>
+          <t>Slab</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'stucco',_'value':_'stucco'}</t>
+          <t>stucco</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Stucco', 'value': 'Stucco'}</t>
+          <t>Stucco</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'vinyl',_'value':_'vinyl'}</t>
+          <t>vinyl</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Vinyl', 'value': 'Vinyl'}</t>
+          <t>Vinyl</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'brick',_'value':_'brick'}</t>
+          <t>brick</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Brick', 'value': 'Brick'}</t>
+          <t>Brick</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'metal',_'value':_'metal'}</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Metal', 'value': 'Metal'}</t>
+          <t>Metal</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'central_ac',_'value':_'central_ac'}</t>
+          <t>central_ac</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Central AC', 'value': 'Central AC'}</t>
+          <t>Central AC</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'heat_pump',_'value':_'heat_pump'}</t>
+          <t>heat_pump</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Heat Pump', 'value': 'Heat Pump'}</t>
+          <t>Heat Pump</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'propane',_'value':_'propane'}</t>
+          <t>propane</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Propane', 'value': 'Propane'}</t>
+          <t>Propane</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'200-amp_service',_'value':_'200-amp_service'}</t>
+          <t>200-amp_service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '200-amp service', 'value': '200-amp service'}</t>
+          <t>200-amp service</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'400-amp_service',_'value':_'400-amp_service'}</t>
+          <t>400-amp_service</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '400-amp service', 'value': '400-amp service'}</t>
+          <t>400-amp service</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'city',_'value':_'city'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'City', 'value': 'City'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'well',_'value':_'well'}</t>
+          <t>well</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Well', 'value': 'Well'}</t>
+          <t>Well</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'smoke_detector',_'value':_'smoke_detector'}</t>
+          <t>smoke_detector</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Smoke Detector', 'value': 'Smoke Detector'}</t>
+          <t>Smoke Detector</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire_alarm',_'value':_'fire_alarm'}</t>
+          <t>fire_alarm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fire Alarm', 'value': 'Fire Alarm'}</t>
+          <t>Fire Alarm</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sprinkler_system',_'value':_'sprinkler_system'}</t>
+          <t>sprinkler_system</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sprinkler System', 'value': 'Sprinkler System'}</t>
+          <t>Sprinkler System</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fire_extinguisher',_'value':_'fire_extinguisher'}</t>
+          <t>fire_extinguisher</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Fire Extinguisher', 'value': 'Fire Extinguisher'}</t>
+          <t>Fire Extinguisher</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire_alarm_system',_'value':_'fire_alarm_system'}</t>
+          <t>fire_alarm_system</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fire Alarm System', 'value': 'Fire Alarm System'}</t>
+          <t>Fire Alarm System</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fire_sprinkler_system',_'value':_'fire_sprinkler_system'}</t>
+          <t>fire_sprinkler_system</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fire Sprinkler System', 'value': 'Fire Sprinkler System'}</t>
+          <t>Fire Sprinkler System</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gate',_'value':_'gate'}</t>
+          <t>gate</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Gate', 'value': 'Gate'}</t>
+          <t>Gate</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'alarm',_'value':_'alarm'}</t>
+          <t>alarm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Alarm', 'value': 'Alarm'}</t>
+          <t>Alarm</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fence',_'value':_'fence'}</t>
+          <t>fence</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fence', 'value': 'Fence'}</t>
+          <t>Fence</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'city',_'value':_'city'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'City', 'value': 'City'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'private',_'value':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Private', 'value': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'well',_'value':_'well'}</t>
+          <t>well</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Well', 'value': 'Well'}</t>
+          <t>Well</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'city',_'value':_'city'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'City', 'value': 'City'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'private',_'value':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Private', 'value': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'city',_'value':_'city'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'City', 'value': 'City'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'private',_'value':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Private', 'value': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'included',_'value':_'included'}</t>
+          <t>included</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Included', 'value': 'Included'}</t>
+          <t>Included</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'separate',_'value':_'separate'}</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Separate', 'value': 'Separate'}</t>
+          <t>Separate</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'included',_'value':_'included'}</t>
+          <t>included</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Included', 'value': 'Included'}</t>
+          <t>Included</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'separate',_'value':_'separate'}</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Separate', 'value': 'Separate'}</t>
+          <t>Separate</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'included',_'value':_'included'}</t>
+          <t>included</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Included', 'value': 'Included'}</t>
+          <t>Included</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'separate',_'value':_'separate'}</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Separate', 'value': 'Separate'}</t>
+          <t>Separate</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
